--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486960_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486960_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6423</v>
+        <v>9.5016</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9243</v>
+        <v>6.2579</v>
       </c>
       <c r="F2" t="n">
-        <v>3.718</v>
+        <v>3.2437</v>
       </c>
       <c r="G2" t="n">
         <v>6.2871</v>
@@ -610,13 +610,13 @@
         <v>3.2855</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4114</v>
+        <v>1.2708</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7509</v>
+        <v>1.0846</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6605</v>
+        <v>0.1862</v>
       </c>
       <c r="V2" t="n">
         <v>0.7117</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.308400000000001</v>
+        <v>7.2236</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9889</v>
+        <v>5.9042</v>
       </c>
       <c r="F3" t="n">
         <v>1.3195</v>
@@ -688,10 +688,10 @@
         <v>3.9015</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2078</v>
+        <v>2.1231</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8512</v>
+        <v>1.7665</v>
       </c>
       <c r="U3" t="n">
         <v>0.3566</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0315</v>
+        <v>2.064</v>
       </c>
       <c r="E4" t="n">
-        <v>0.869</v>
+        <v>1.6217</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1625</v>
+        <v>0.4423</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2981</v>
+        <v>1.7365</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9797</v>
+        <v>0.9893</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3184</v>
+        <v>0.7472</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9349</v>
+        <v>3.1406</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8954</v>
+        <v>1.9305</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0395</v>
+        <v>1.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3632</v>
+        <v>-1.4041</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0843</v>
+        <v>-0.9412</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2789</v>
+        <v>-0.4629</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.6694</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0263</v>
+        <v>0.8901</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0659</v>
+        <v>0.5345</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0395</v>
+        <v>0.3556</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7512</v>
+        <v>1.0908</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5756</v>
+        <v>0.869</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1756</v>
+        <v>0.2218</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7365</v>
+        <v>1.2981</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9893</v>
+        <v>0.9797</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7472</v>
+        <v>0.3184</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1406</v>
+        <v>0.9349</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9305</v>
+        <v>0.8954</v>
       </c>
       <c r="L5" t="n">
-        <v>1.21</v>
+        <v>0.0395</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4041</v>
+        <v>0.3632</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9412</v>
+        <v>0.0843</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4629</v>
+        <v>0.2789</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6694</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4227</v>
+        <v>0.0329</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5115</v>
+        <v>-0.0659</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0888</v>
+        <v>0.0988</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2789</v>
+        <v>0.3295</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1.7584</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2789</v>
+        <v>-1.4289</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2789</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.3273</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2789</v>
+        <v>-0.2448</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.2266</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.7534</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.4732</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2789</v>
+        <v>-1.7987</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.0807</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2789</v>
+        <v>-0.7181</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.0267</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.0801</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.3419</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.2352</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.4669</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.0082</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.4751</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2683</v>
+        <v>0.2789</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0644</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7961</v>
+        <v>0.2789</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.135</v>
+        <v>0.2789</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7096</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8445</v>
+        <v>0.2789</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0744</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4561</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3817</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2094</v>
+        <v>0.2789</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7465000000000001</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4629</v>
+        <v>0.2789</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0534</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0155</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0854</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0699</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1179</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3406</v>
+        <v>0.0242</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5317</v>
+        <v>-0.4755</v>
       </c>
       <c r="F8" t="n">
-        <v>0.191</v>
+        <v>0.4997</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.3079</v>
+        <v>-0.135</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9369</v>
+        <v>1.7096</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3709</v>
+        <v>-1.8445</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1436</v>
+        <v>1.0744</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0249</v>
+        <v>2.4561</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1188</v>
+        <v>-1.3817</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1643</v>
+        <v>-1.2094</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9121</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2522</v>
+        <v>-0.4629</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0801</v>
+        <v>-0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>3.0801</v>
+        <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8345</v>
+        <v>0.277</v>
       </c>
       <c r="T8" t="n">
-        <v>0.612</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2226</v>
+        <v>-0.2265</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9474</v>
+        <v>-0.1179</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9474</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.401</v>
+        <v>-0.348</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2354</v>
+        <v>-0.3612</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6364</v>
+        <v>0.0132</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-3.3079</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3273</v>
+        <v>-1.9369</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2448</v>
+        <v>-1.3709</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2266</v>
+        <v>-1.1436</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7534</v>
+        <v>-1.0249</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4732</v>
+        <v>-0.1188</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7987</v>
+        <v>-2.1643</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0807</v>
+        <v>-0.9121</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7181</v>
+        <v>-1.2522</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0267</v>
+        <v>3.0801</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>3.0801</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3886</v>
+        <v>0.8272</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0541</v>
+        <v>0.7824</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4427</v>
+        <v>0.0447</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4669</v>
+        <v>-0.9474</v>
       </c>
       <c r="W9" t="n">
-        <v>2.0082</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4751</v>
+        <v>-0.9474</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4693</v>
+        <v>-1.5606</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8793</v>
+        <v>-3.0299</v>
       </c>
       <c r="F10" t="n">
-        <v>1.41</v>
+        <v>1.4693</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9232</v>
@@ -1234,13 +1234,13 @@
         <v>2.4641</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1316</v>
+        <v>1.0402</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5491</v>
+        <v>1.3985</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4175</v>
+        <v>-0.3582</v>
       </c>
       <c r="V10" t="n">
         <v>0.9384</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6386</v>
+        <v>-4.3802</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0256</v>
+        <v>-5.1229</v>
       </c>
       <c r="F11" t="n">
-        <v>0.387</v>
+        <v>0.7427</v>
       </c>
       <c r="G11" t="n">
         <v>-4.2166</v>
@@ -1312,13 +1312,13 @@
         <v>2.0534</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.456</v>
+        <v>-0.1976</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7827</v>
+        <v>0.12</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6733</v>
+        <v>-0.3176</v>
       </c>
       <c r="V11" t="n">
         <v>1.0608</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.8945</v>
+        <v>14.2238</v>
       </c>
       <c r="E12" t="n">
-        <v>7.092199999999999</v>
+        <v>7.421700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>6.802199999999999</v>
+        <v>6.8022</v>
       </c>
       <c r="G12" t="n">
         <v>1.260900000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>6.958599999999998</v>
+        <v>6.9586</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.697500000000001</v>
+        <v>-5.6975</v>
       </c>
       <c r="J12" t="n">
         <v>9.8565</v>
@@ -1390,13 +1390,13 @@
         <v>22.5875</v>
       </c>
       <c r="S12" t="n">
-        <v>6.276200000000001</v>
+        <v>6.605600000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>6.3718</v>
+        <v>6.7012</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.09560000000000002</v>
+        <v>-0.09560000000000007</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8294000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1226</v>
+        <v>5.7903</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8977</v>
+        <v>4.3161</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2249</v>
+        <v>1.4742</v>
       </c>
       <c r="G13" t="n">
         <v>3.467</v>
@@ -1468,13 +1468,13 @@
         <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6934</v>
+        <v>-1.0257</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9145</v>
+        <v>-0.4961</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7789</v>
+        <v>-0.5296</v>
       </c>
       <c r="V13" t="n">
         <v>2.117</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.708</v>
+        <v>-0.1659</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7917999999999999</v>
+        <v>-0.1046</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0838</v>
+        <v>-0.0612</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0936</v>
+        <v>-1.4277</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2197</v>
+        <v>-2.9646</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1261</v>
+        <v>1.5369</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6057</v>
+        <v>-0.0558</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1057</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5</v>
+        <v>0.605</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5121</v>
+        <v>-1.372</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.886</v>
+        <v>-2.3038</v>
       </c>
       <c r="O14" t="n">
-        <v>0.374</v>
+        <v>0.9318</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.2855</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.1336</v>
+        <v>-3.0801</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4194</v>
+        <v>-0.1385</v>
       </c>
       <c r="T14" t="n">
-        <v>3.599</v>
+        <v>0.1936</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1796</v>
+        <v>-0.332</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4805</v>
+        <v>2.8377</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7207</v>
+        <v>2.8377</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>M. ALVAREZ PUERTAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5964</v>
+        <v>-0.3986</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.523</v>
+        <v>-1.7366</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07340000000000001</v>
+        <v>1.338</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4277</v>
+        <v>-2.0045</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.9646</v>
+        <v>-0.7232</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5369</v>
+        <v>-1.2813</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0558</v>
+        <v>-1.7132</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.4764</v>
       </c>
       <c r="L15" t="n">
-        <v>0.605</v>
+        <v>-1.2368</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.372</v>
+        <v>-0.2913</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.3038</v>
+        <v>-0.2468</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9318</v>
+        <v>-0.0445</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.0801</v>
+        <v>-0.2053</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.569</v>
+        <v>-0.0368</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2249</v>
+        <v>0.182</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3442</v>
+        <v>-0.2188</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8377</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8377</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ALVAREZ PUERTAS</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6671</v>
+        <v>-0.4633</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.9458</v>
+        <v>0.0163</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2787</v>
+        <v>-0.4796</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0045</v>
+        <v>-0.8943</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7232</v>
+        <v>0.0712</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2813</v>
+        <v>-0.9656</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.7132</v>
+        <v>0.0629</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4764</v>
+        <v>0.6813</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2368</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2913</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2468</v>
+        <v>-0.6101</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0445</v>
+        <v>-0.3472</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8481</v>
+        <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3053</v>
+        <v>-0.3904</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0272</v>
+        <v>-0.0466</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.278</v>
+        <v>-0.3438</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0404</v>
+        <v>-0.9569</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1929</v>
+        <v>-1.3002</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8475</v>
+        <v>0.3433</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8943</v>
+        <v>1.0936</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0712</v>
+        <v>1.2197</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9656</v>
+        <v>-0.1261</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0629</v>
+        <v>1.6057</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6813</v>
+        <v>2.1057</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.5121</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6101</v>
+        <v>-0.886</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3472</v>
+        <v>0.374</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8214</v>
+        <v>-3.2855</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-5.1336</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9674</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2558</v>
+        <v>1.5069</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7117</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.7207</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PARRA BAEZ</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6805</v>
+        <v>-1.0012</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.187</v>
+        <v>0.3894</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4935</v>
+        <v>-1.3906</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0243</v>
+        <v>-0.2006</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1053</v>
+        <v>-1.3532</v>
       </c>
       <c r="I18" t="n">
-        <v>2.081</v>
+        <v>1.1525</v>
       </c>
       <c r="J18" t="n">
-        <v>1.858</v>
+        <v>1.5897</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2199</v>
+        <v>1.0901</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0779</v>
+        <v>0.4997</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8823</v>
+        <v>-1.7904</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8854</v>
+        <v>-2.4433</v>
       </c>
       <c r="O18" t="n">
-        <v>0.003</v>
+        <v>0.6529</v>
       </c>
       <c r="P18" t="n">
         <v>-0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2855</v>
+        <v>-2.2588</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4641</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8348</v>
+        <v>-0.5686</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3489</v>
+        <v>-0.1203</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4859</v>
+        <v>-0.4483</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5893</v>
+        <v>1.1786</v>
       </c>
       <c r="X18" t="n">
         <v>-0.5893</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>J. PARRA BAEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8294</v>
+        <v>-1.637</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2848</v>
+        <v>-0.9778</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1142</v>
+        <v>-0.6592</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2006</v>
+        <v>-0.0243</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3532</v>
+        <v>-2.1053</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1525</v>
+        <v>2.081</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5897</v>
+        <v>1.858</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0901</v>
+        <v>-0.2199</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4997</v>
+        <v>2.0779</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7904</v>
+        <v>-1.8823</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.4433</v>
+        <v>-1.8854</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6529</v>
+        <v>0.003</v>
       </c>
       <c r="P19" t="n">
         <v>-0.8214</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2588</v>
+        <v>-3.2855</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4374</v>
+        <v>2.4641</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3967</v>
+        <v>-0.7913</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2249</v>
+        <v>-0.1397</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1719</v>
+        <v>-0.6516</v>
       </c>
       <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
         <v>0.5893</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.1786</v>
       </c>
       <c r="X19" t="n">
         <v>-0.5893</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2407</v>
+        <v>-2.1902</v>
       </c>
       <c r="E20" t="n">
         <v>0.1816</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4223</v>
+        <v>-2.3718</v>
       </c>
       <c r="G20" t="n">
         <v>0.7449</v>
@@ -2014,13 +2014,13 @@
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9774</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="T20" t="n">
         <v>-0.7905</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.187</v>
+        <v>-0.1364</v>
       </c>
       <c r="V20" t="n">
         <v>-2.0082</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4857</v>
+        <v>-4.1231</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9359</v>
+        <v>-2.8313</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5499</v>
+        <v>-1.2918</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1708</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0213</v>
+        <v>-0.6586</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2635</v>
+        <v>-0.1589</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7578</v>
+        <v>-0.4997</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2402</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.1848</v>
+        <v>-6.6566</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.1734</v>
+        <v>-4.755</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0114</v>
+        <v>-1.9016</v>
       </c>
       <c r="G22" t="n">
         <v>-0.844</v>
@@ -2170,13 +2170,13 @@
         <v>1.8481</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9302</v>
+        <v>-0.4019</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4534</v>
+        <v>-0.035</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4768</v>
+        <v>-0.367</v>
       </c>
       <c r="V22" t="n">
         <v>-2.9466</v>
@@ -2203,28 +2203,28 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-13.8944</v>
+        <v>-11.8025</v>
       </c>
       <c r="E23" t="n">
         <v>-6.8021</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.0924</v>
+        <v>-5.0003</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2607</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.9585</v>
+        <v>-6.958500000000001</v>
       </c>
       <c r="I23" t="n">
         <v>5.6976</v>
       </c>
       <c r="J23" t="n">
-        <v>8.595499999999999</v>
+        <v>8.595500000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>5.2429</v>
+        <v>5.242900000000001</v>
       </c>
       <c r="L23" t="n">
         <v>3.3528</v>
@@ -2248,19 +2248,19 @@
         <v>15.4008</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.2761</v>
+        <v>-4.184200000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.09540000000000015</v>
+        <v>0.09539999999999987</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.371799999999999</v>
+        <v>-4.2797</v>
       </c>
       <c r="V23" t="n">
         <v>0.8294999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>7.0942</v>
+        <v>7.094200000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-6.2647</v>
